--- a/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_23_9.xlsx
+++ b/fuction_ensemble/redes-ensemble-s/Teste05/content/results/metrics_23_9.xlsx
@@ -513,1321 +513,1321 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_5</t>
+          <t>model_23_9_0</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.9960272394169192</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C2" t="n">
-        <v>0.809600328285042</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D2" t="n">
-        <v>0.995301661460789</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9617414975815515</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9755893480429456</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G2" t="n">
-        <v>0.02656586831194159</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H2" t="n">
-        <v>1.273203481467799</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I2" t="n">
-        <v>0.01038446158937789</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J2" t="n">
-        <v>0.1206825286028069</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>0.06553349146399938</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2354681083829902</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1629903933118194</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N2" t="n">
-        <v>1.000829097860817</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1699292317917309</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P2" t="n">
-        <v>285.256256066598</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q2" t="n">
-        <v>454.6799957232779</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_4</t>
+          <t>model_23_9_22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.9957753152346029</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8095952592056536</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9962339019877745</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9603503026156424</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9751557870669488</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02825048647909469</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H3" t="n">
-        <v>1.27323737842501</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I3" t="n">
-        <v>0.008323985132913603</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1250709106787462</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0666974408976153</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2286190141615124</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1680788103215116</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N3" t="n">
-        <v>1.000881673342344</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1752342732480011</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P3" t="n">
-        <v>285.1332892020781</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q3" t="n">
-        <v>454.5570288587579</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_6</t>
+          <t>model_23_9_21</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.9962259624622254</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C4" t="n">
-        <v>0.8095721585152714</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9943505831461953</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9629347260437876</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F4" t="n">
-        <v>0.97589886692524</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0252370063929436</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H4" t="n">
-        <v>1.273391852847964</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I4" t="n">
-        <v>0.01248657410084598</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J4" t="n">
-        <v>0.1169186115929749</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06470254876462078</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2414069499010306</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1588615950849783</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N4" t="n">
-        <v>1.000787625225275</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1656246620765826</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P4" t="n">
-        <v>285.3588877080223</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q4" t="n">
-        <v>454.7826273647022</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_3</t>
+          <t>model_23_9_20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.9954569408608513</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8095446153621748</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9971168293194247</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E5" t="n">
-        <v>0.9587226530920975</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9745630108522071</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03037945738235055</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H5" t="n">
-        <v>1.273576034039546</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I5" t="n">
-        <v>0.006372502734356568</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J5" t="n">
-        <v>0.1302051644462389</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0682888238347521</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2207470362464267</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M5" t="n">
-        <v>0.174297037789948</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N5" t="n">
-        <v>1.000948116689909</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1817172235332741</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P5" t="n">
-        <v>284.987977285979</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q5" t="n">
-        <v>454.4117169426588</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_7</t>
+          <t>model_23_9_19</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.996382181172413</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C6" t="n">
-        <v>0.8095204497526007</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9934034513400084</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E6" t="n">
-        <v>0.9639620493411709</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F6" t="n">
-        <v>0.9761124936967971</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G6" t="n">
-        <v>0.02419237115859888</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H6" t="n">
-        <v>1.27373762958204</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I6" t="n">
-        <v>0.01457996387668733</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1136780254386929</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06412904059962199</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2465559112878023</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1555389699033618</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N6" t="n">
-        <v>1.00075502305967</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1621605858622023</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P6" t="n">
-        <v>285.4434358737975</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q6" t="n">
-        <v>454.8671755304773</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_8</t>
+          <t>model_23_9_18</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.9965044466670175</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C7" t="n">
-        <v>0.809452617501537</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9924770062161463</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9648491913669561</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F7" t="n">
-        <v>0.976252335261479</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02337478123319685</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H7" t="n">
-        <v>1.274191224157243</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01662763109417748</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1108796267525501</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06375361818151019</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2510188362533748</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M7" t="n">
-        <v>0.1528881330685834</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N7" t="n">
-        <v>1.000729506782535</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O7" t="n">
-        <v>0.1593968974153787</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P7" t="n">
-        <v>285.5121951257176</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q7" t="n">
-        <v>454.9359347823975</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_2</t>
+          <t>model_23_9_17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.9950556318147111</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8094326622511447</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D8" t="n">
-        <v>0.9979107268018953</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9568107875846689</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9737666051005075</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G8" t="n">
-        <v>0.03306301282174872</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H8" t="n">
-        <v>1.274324665008501</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I8" t="n">
-        <v>0.004617797779867632</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J8" t="n">
-        <v>0.1362359484341067</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>0.07042687609254118</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>0.211700402030608</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1818323756148743</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N8" t="n">
-        <v>1.001031868143017</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1895733562897072</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P8" t="n">
-        <v>284.8186801176144</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q8" t="n">
-        <v>454.2424197742943</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_9</t>
+          <t>model_23_9_16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.996599685838687</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C9" t="n">
-        <v>0.8093743841482238</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9915830807390895</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E9" t="n">
-        <v>0.9656180042162598</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9763360114510704</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02273791645370705</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H9" t="n">
-        <v>1.274714370951079</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I9" t="n">
-        <v>0.01860342204725375</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J9" t="n">
-        <v>0.1084544853379308</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06352897883693341</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>0.2548895882292725</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1507909694036982</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N9" t="n">
-        <v>1.000709630781491</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O9" t="n">
-        <v>0.1572104531515521</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P9" t="n">
-        <v>285.5674428391692</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q9" t="n">
-        <v>454.991182495849</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_10</t>
+          <t>model_23_9_15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.9966734549943349</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C10" t="n">
-        <v>0.8092901721610968</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9907298441046553</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E10" t="n">
-        <v>0.966286460487454</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9763774760353295</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G10" t="n">
-        <v>0.02224462177021392</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H10" t="n">
-        <v>1.275277496896758</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I10" t="n">
-        <v>0.02048928084243981</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J10" t="n">
-        <v>0.1063459084734784</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K10" t="n">
-        <v>0.06341766190105694</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2582420274586024</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1491463099450131</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N10" t="n">
-        <v>1.000694235479443</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O10" t="n">
-        <v>0.1554957771347964</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P10" t="n">
-        <v>285.6113100355622</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q10" t="n">
-        <v>455.035049692242</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_1</t>
+          <t>model_23_9_14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.9945510964532844</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8092395258733283</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9985645158987646</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9545576582934657</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F11" t="n">
-        <v>0.9727120376409937</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G11" t="n">
-        <v>0.03643684310678109</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>1.275616168856271</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I11" t="n">
-        <v>0.003172766157022094</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1433432140859979</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K11" t="n">
-        <v>0.07325799620059242</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2013349440544251</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M11" t="n">
-        <v>0.1908843710385454</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N11" t="n">
-        <v>1.001137162479315</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O11" t="n">
-        <v>0.1990107138987778</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P11" t="n">
-        <v>284.6243496859564</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q11" t="n">
-        <v>454.0480893426362</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_11</t>
+          <t>model_23_9_13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.9967301856815581</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8092032004748195</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9899224553034681</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9668693604074683</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F12" t="n">
-        <v>0.9763875756816095</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G12" t="n">
-        <v>0.02186526340353145</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H12" t="n">
-        <v>1.275859076963362</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02227380486591061</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J12" t="n">
-        <v>0.1045072103587355</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K12" t="n">
-        <v>0.06339054811956372</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L12" t="n">
-        <v>0.2611515862597827</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M12" t="n">
-        <v>0.1478690752102395</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N12" t="n">
-        <v>1.000682396031675</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O12" t="n">
-        <v>0.154164167873123</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P12" t="n">
-        <v>285.6457120947568</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q12" t="n">
-        <v>455.0694517514366</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_12</t>
+          <t>model_23_9_23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.9967734452277264</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C13" t="n">
-        <v>0.8091159615214949</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D13" t="n">
-        <v>0.9891638196358726</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E13" t="n">
-        <v>0.9673791667436484</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F13" t="n">
-        <v>0.97637479419833</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G13" t="n">
-        <v>0.02157598661911211</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H13" t="n">
-        <v>1.276442444245942</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I13" t="n">
-        <v>0.02395057270303654</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J13" t="n">
-        <v>0.1028990784701678</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K13" t="n">
-        <v>0.06342486163265092</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L13" t="n">
-        <v>0.2636804401117193</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M13" t="n">
-        <v>0.1468876666678047</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N13" t="n">
-        <v>1.000673367952474</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1531409787372411</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P13" t="n">
-        <v>285.6723486266391</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q13" t="n">
-        <v>455.0960882833189</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_13</t>
+          <t>model_23_9_12</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.9968060454777297</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8090301510521032</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9884551653531886</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9678258014264105</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9763454781339751</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0213579885972297</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>1.277016259249885</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I14" t="n">
-        <v>0.02551686962209944</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1014902150941814</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K14" t="n">
-        <v>0.06350356432590697</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2658799167931459</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M14" t="n">
-        <v>0.1461437258223209</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N14" t="n">
-        <v>1.000666564422039</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1523653667897951</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P14" t="n">
-        <v>285.6926588722409</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q14" t="n">
-        <v>455.1163985289208</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_14</t>
+          <t>model_23_9_10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.9968303202429157</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C15" t="n">
-        <v>0.8089470808900641</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9877965396545797</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9682184992981154</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9763050635903937</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G15" t="n">
-        <v>0.02119566313065574</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>1.277571749805944</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I15" t="n">
-        <v>0.02697259130156135</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J15" t="n">
-        <v>0.1002514898661015</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0636120622943952</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L15" t="n">
-        <v>0.2677925163430481</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1455873041534039</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N15" t="n">
-        <v>1.000661498384087</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O15" t="n">
-        <v>0.1517852570984807</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P15" t="n">
-        <v>285.7079173750801</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q15" t="n">
-        <v>455.1316570317599</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_0</t>
+          <t>model_23_9_9</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.993918200485763</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C16" t="n">
-        <v>0.8089400834157701</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D16" t="n">
-        <v>0.9990131100805686</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9518930725490308</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9713312764611768</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G16" t="n">
-        <v>0.04066902135581484</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>1.277618541948769</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I16" t="n">
-        <v>0.002181264797279003</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J16" t="n">
-        <v>0.1517483769907107</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K16" t="n">
-        <v>0.07696482472571943</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1895074927062522</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M16" t="n">
-        <v>0.2016656176838651</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N16" t="n">
-        <v>1.001269245116015</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O16" t="n">
-        <v>0.2102509405340459</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P16" t="n">
-        <v>284.4045772448022</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q16" t="n">
-        <v>453.828316901482</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_15</t>
+          <t>model_23_9_8</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.9968480367116053</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8088675862963297</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9871867556815631</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9685643468934598</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F17" t="n">
-        <v>0.9762572576498272</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G17" t="n">
-        <v>0.02107719302295165</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>1.278103330520284</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I17" t="n">
-        <v>0.02832036098498485</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J17" t="n">
-        <v>0.09916054903781532</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K17" t="n">
-        <v>0.06374040340562614</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2694614663348724</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M17" t="n">
-        <v>0.1451798643853604</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0006578010341</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O17" t="n">
-        <v>0.151360471775995</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P17" t="n">
-        <v>285.7191274449586</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q17" t="n">
-        <v>455.1428671016385</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_16</t>
+          <t>model_23_9_7</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.9968606256749981</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8087922153600887</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D18" t="n">
-        <v>0.9866242201459985</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E18" t="n">
-        <v>0.968869221641541</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9762048076749614</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G18" t="n">
-        <v>0.02099301056677697</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>1.278607336317979</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I18" t="n">
-        <v>0.02956370022352169</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J18" t="n">
-        <v>0.09819885286102437</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K18" t="n">
-        <v>0.06388121201599037</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L18" t="n">
-        <v>0.2709176057609319</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1448896496192084</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N18" t="n">
-        <v>1.000655173772174</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1510579019664205</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P18" t="n">
-        <v>285.7271314536249</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q18" t="n">
-        <v>455.1508711103048</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_17</t>
+          <t>model_23_9_6</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.9968692837925984</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C19" t="n">
-        <v>0.8087213602486627</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D19" t="n">
-        <v>0.9861070614213256</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E19" t="n">
-        <v>0.9691388836561646</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9761503205521435</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G19" t="n">
-        <v>0.02093511369451678</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H19" t="n">
-        <v>1.279081144774342</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I19" t="n">
-        <v>0.03070674576337732</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J19" t="n">
-        <v>0.09734823164650386</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K19" t="n">
-        <v>0.06402748960842711</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2721958841219962</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M19" t="n">
-        <v>0.1446897152340718</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N19" t="n">
-        <v>1.000653366860675</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1508494559605874</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P19" t="n">
-        <v>285.7326548973829</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q19" t="n">
-        <v>455.1563945540627</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_18</t>
+          <t>model_23_9_5</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.9968749031271019</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8086550745505292</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9856325138058989</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E20" t="n">
-        <v>0.9693777958801871</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F20" t="n">
-        <v>0.9760953438376838</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G20" t="n">
-        <v>0.02089753717881722</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>1.279524397542979</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I20" t="n">
-        <v>0.0317556104723808</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J20" t="n">
-        <v>0.09659460749797356</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K20" t="n">
-        <v>0.06417508157172654</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2733079350014388</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M20" t="n">
-        <v>0.1445598048518924</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N20" t="n">
-        <v>1.000652194129996</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1507140150244871</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P20" t="n">
-        <v>285.7362479305779</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q20" t="n">
-        <v>455.1599875872578</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_19</t>
+          <t>model_23_9_4</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.9968781897758674</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C21" t="n">
-        <v>0.808593386625486</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D21" t="n">
-        <v>0.9851981823365142</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E21" t="n">
-        <v>0.9695895804049288</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F21" t="n">
-        <v>0.9760409593137419</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G21" t="n">
-        <v>0.02087555934338917</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H21" t="n">
-        <v>1.27993690498179</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I21" t="n">
-        <v>0.03271558779696941</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J21" t="n">
-        <v>0.09592655489922761</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0643210837244665</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L21" t="n">
-        <v>0.2742910499105348</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1444837684426495</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N21" t="n">
-        <v>1.000651508220689</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1506347415878857</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P21" t="n">
-        <v>285.7383524274226</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q21" t="n">
-        <v>455.1620920841025</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_20</t>
+          <t>model_23_9_3</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.9968797091214436</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C22" t="n">
-        <v>0.8085362708425802</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D22" t="n">
-        <v>0.9848013468418081</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E22" t="n">
-        <v>0.9697775384653253</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F22" t="n">
-        <v>0.9759880483842057</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G22" t="n">
-        <v>0.02086539947252506</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>1.280318838485075</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I22" t="n">
-        <v>0.03359268997206506</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J22" t="n">
-        <v>0.09533366044267431</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K22" t="n">
-        <v>0.06446312982611155</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L22" t="n">
-        <v>0.2751491617576015</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M22" t="n">
-        <v>0.1444486049518134</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N22" t="n">
-        <v>1.000651191139873</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1505980811144462</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P22" t="n">
-        <v>285.7393260390839</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q22" t="n">
-        <v>455.1630656957638</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_21</t>
+          <t>model_23_9_2</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.9968799542957384</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C23" t="n">
-        <v>0.8084835342427339</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D23" t="n">
-        <v>0.9844394842914044</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E23" t="n">
-        <v>0.9699450407077832</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F23" t="n">
-        <v>0.9759375064046298</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G23" t="n">
-        <v>0.02086375999088705</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H23" t="n">
-        <v>1.280671488371077</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I23" t="n">
-        <v>0.03439249350344975</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J23" t="n">
-        <v>0.09480529176934352</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K23" t="n">
-        <v>0.06459881618110667</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L23" t="n">
-        <v>0.2759070275831219</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1444429298750446</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N23" t="n">
-        <v>1.000651139973063</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O23" t="n">
-        <v>0.1505921644379103</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P23" t="n">
-        <v>285.7394831936166</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q23" t="n">
-        <v>455.1632228502965</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_22</t>
+          <t>model_23_9_1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.9968792045986171</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C24" t="n">
-        <v>0.8084350411490614</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D24" t="n">
-        <v>0.9841099857062291</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9700936490563715</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F24" t="n">
-        <v>0.9758891487881984</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G24" t="n">
-        <v>0.02086877321898897</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>1.280995761911755</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I24" t="n">
-        <v>0.03512076486426192</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J24" t="n">
-        <v>0.09433652194968448</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K24" t="n">
-        <v>0.06472863833617255</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L24" t="n">
-        <v>0.276576137270854</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1444602824965706</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N24" t="n">
-        <v>1.000651296431593</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O24" t="n">
-        <v>0.1506102557964595</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P24" t="n">
-        <v>285.7390026833058</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q24" t="n">
-        <v>455.1627423399857</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>model_23_9_23</t>
+          <t>model_23_9_11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.996877805541443</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C25" t="n">
-        <v>0.8083904851028449</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D25" t="n">
-        <v>0.9838101847265944</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E25" t="n">
-        <v>0.9702265970512586</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F25" t="n">
-        <v>0.9758438438651111</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G25" t="n">
-        <v>0.02087812872075445</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H25" t="n">
-        <v>1.281293708397967</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I25" t="n">
-        <v>0.03578339735263859</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J25" t="n">
-        <v>0.09391715111231708</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K25" t="n">
-        <v>0.06485026514874763</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L25" t="n">
-        <v>0.2771654075206589</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1444926597469728</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N25" t="n">
-        <v>1.000651588408742</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O25" t="n">
-        <v>0.1506440114134415</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P25" t="n">
-        <v>285.7381062812748</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q25" t="n">
-        <v>455.1618459379546</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
     <row r="26">
@@ -1837,52 +1837,52 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.9968759405329853</v>
+        <v>0.9999741335627697</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8083497439958808</v>
+        <v>0.6467963933326112</v>
       </c>
       <c r="D26" t="n">
-        <v>0.9835381062982318</v>
+        <v>0.9999999999962464</v>
       </c>
       <c r="E26" t="n">
-        <v>0.9703450882277445</v>
+        <v>0.9999972769139674</v>
       </c>
       <c r="F26" t="n">
-        <v>0.9758014366214093</v>
+        <v>0.9999995590172681</v>
       </c>
       <c r="G26" t="n">
-        <v>0.02089060004089805</v>
+        <v>1.535543451182101e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>1.281566144367831</v>
+        <v>0.2096769185191193</v>
       </c>
       <c r="I26" t="n">
-        <v>0.03638475631497177</v>
+        <v>6.468220886456369e-13</v>
       </c>
       <c r="J26" t="n">
-        <v>0.09354338282836694</v>
+        <v>2.589119095747892e-07</v>
       </c>
       <c r="K26" t="n">
-        <v>0.06496411277346642</v>
+        <v>1.294562543894273e-07</v>
       </c>
       <c r="L26" t="n">
-        <v>0.2776902827139426</v>
+        <v>0.001328529658592125</v>
       </c>
       <c r="M26" t="n">
-        <v>0.1445358088533705</v>
+        <v>0.003918601091183053</v>
       </c>
       <c r="N26" t="n">
-        <v>1.000651977627899</v>
+        <v>1.000010891131465</v>
       </c>
       <c r="O26" t="n">
-        <v>0.1506889974666295</v>
+        <v>0.00408542405225724</v>
       </c>
       <c r="P26" t="n">
-        <v>285.7369119599838</v>
+        <v>184.1680822134607</v>
       </c>
       <c r="Q26" t="n">
-        <v>455.1606516166636</v>
+        <v>282.8970240277849</v>
       </c>
     </row>
   </sheetData>
